--- a/ER参考図.xlsx
+++ b/ER参考図.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lon\Desktop\SpringOuyo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8C3F11-BBA3-476F-8004-EB0D64E326E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="1056" yWindow="180" windowWidth="20028" windowHeight="11592" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -20,69 +28,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
-  <si>
-    <t xml:space="preserve">Users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Messages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTO_INCREMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">user_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT NULL, UNIQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">product_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Products.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">password</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>Messages</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Long</t>
+  </si>
+  <si>
+    <t>AUTO_INCREMENT</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>NOT NULL, UNIQUE</t>
+  </si>
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>Products.id</t>
+  </si>
+  <si>
+    <t>password</t>
   </si>
   <si>
     <t xml:space="preserve">NOT NULL </t>
   </si>
   <si>
-    <t xml:space="preserve">sender_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Users.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nickname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">receiver_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT NULL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">create_at</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LocalDateTime</t>
+    <t>sender_id</t>
+  </si>
+  <si>
+    <t>Users.id</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>receiver_id</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>NOT NULL</t>
+  </si>
+  <si>
+    <t>create_at</t>
+  </si>
+  <si>
+    <t>LocalDateTime</t>
   </si>
   <si>
     <r>
@@ -99,17 +107,17 @@
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">初期現在の日時</t>
+      <t>初期現在の日時</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boolean</t>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>is_read</t>
+  </si>
+  <si>
+    <t>Boolean</t>
   </si>
   <si>
     <r>
@@ -126,29 +134,26 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">False</t>
+      <t>False</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">product_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User_Favorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status</t>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>User_Favorite</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>Int</t>
+  </si>
+  <si>
+    <t>status</t>
   </si>
   <si>
     <r>
@@ -165,7 +170,7 @@
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">初期</t>
+      <t>初期</t>
     </r>
     <r>
       <rPr>
@@ -173,24 +178,53 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">OPEN</t>
+      <t>OPEN</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">seller_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">buyer_id</t>
+    <t>seller_id</t>
+  </si>
+  <si>
+    <t>buyer_id</t>
+  </si>
+  <si>
+    <t>Category</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>BigCategory</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>MidCategory</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>SmallCategory</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>INT(5)</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>VARCHAR(50)</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>category_id</t>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK JP"/>
@@ -199,17 +233,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -217,38 +241,45 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
-      <i val="true"/>
+      <b/>
+      <i/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="10"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Noto Serif CJK JP"/>
-      <family val="1"/>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="Noto Serif CJK JP"/>
+      <b/>
+      <sz val="10"/>
+      <name val="Noto Sans CJK JP"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -261,93 +292,63 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -361,9 +362,15 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>183600</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="線 1"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="線 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -381,9 +388,15 @@
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -402,9 +415,15 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>191880</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="テキスト枠 1"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="テキスト枠 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -424,6 +443,7 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
@@ -433,38 +453,92 @@
             </a:rPr>
             <a:t>1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif CJK JP"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>268200</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>154440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>418320</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>10080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="線 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="1342080" y="1129680"/>
+          <a:ext cx="150120" cy="54000"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465A4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>924480</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>41760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>155880</xdr:colOff>
+      <xdr:colOff>419760</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>51480</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>345240</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>72720</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="テキスト枠 2"/>
+      <xdr:rowOff>62640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト枠 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1229760" y="1225080"/>
-          <a:ext cx="189360" cy="219240"/>
+          <a:off x="924480" y="1017000"/>
+          <a:ext cx="569160" cy="219240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -478,101 +552,7 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Noto Serif CJK JP"/>
-            </a:rPr>
-            <a:t>*</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif CJK JP"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>268200</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>154440</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>418320</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>10080</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="線 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="1342080" y="1129680"/>
-          <a:ext cx="150120" cy="54000"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="3465A4"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>924480</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>41760</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>419760</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>62640</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="テキスト枠 3"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="924480" y="1017000"/>
-          <a:ext cx="569160" cy="219240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" sz="1050" b="0" u="none" strike="noStrike">
@@ -605,9 +585,15 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>191160</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="線 3"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="線 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -625,9 +611,15 @@
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -646,9 +638,15 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>179280</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="テキスト枠 4"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="テキスト枠 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -668,6 +666,7 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
@@ -677,11 +676,6 @@
             </a:rPr>
             <a:t>1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif CJK JP"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -691,24 +685,30 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>938520</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>169920</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1123</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>280440</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>190800</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="テキスト枠 5"/>
+      <xdr:rowOff>167940</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="テキスト枠 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2012400" y="1145160"/>
-          <a:ext cx="317880" cy="219240"/>
+          <a:off x="1980242" y="1182705"/>
+          <a:ext cx="296831" cy="166817"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -722,6 +722,7 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
@@ -731,11 +732,6 @@
             </a:rPr>
             <a:t>0..*</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif CJK JP"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -754,9 +750,15 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>59400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="線 4"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="線 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -774,9 +776,15 @@
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -795,9 +803,15 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="テキスト枠 6"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="テキスト枠 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -817,6 +831,7 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" sz="1050" b="0" u="none" strike="noStrike">
@@ -849,9 +864,15 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>195120</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="線 5"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="線 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -869,9 +890,15 @@
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -890,9 +917,15 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>155160</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="テキスト枠 7"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="テキスト枠 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -912,6 +945,7 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
@@ -921,11 +955,6 @@
             </a:rPr>
             <a:t>0..*</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif CJK JP"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -936,23 +965,29 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>47160</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>95400</xdr:rowOff>
+      <xdr:rowOff>109868</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>236520</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>116640</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="テキスト枠 8"/>
+      <xdr:rowOff>131108</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="テキスト枠 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3799440" y="1269000"/>
-          <a:ext cx="189360" cy="219240"/>
+          <a:off x="3698008" y="1291450"/>
+          <a:ext cx="189360" cy="190038"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -966,6 +1001,7 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
@@ -975,11 +1011,6 @@
             </a:rPr>
             <a:t>1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif CJK JP"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -998,9 +1029,15 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>135000</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="線 6"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="線 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1018,9 +1055,15 @@
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -1039,9 +1082,15 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>24120</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="テキスト枠 9"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="テキスト枠 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1061,6 +1110,7 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
@@ -1070,11 +1120,6 @@
             </a:rPr>
             <a:t>1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif CJK JP"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1083,24 +1128,83 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>682200</xdr:colOff>
+      <xdr:colOff>7920</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>83520</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>58680</xdr:colOff>
+      <xdr:rowOff>154080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>801000</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>150480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="線 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3760200" y="966960"/>
+          <a:ext cx="793080" cy="880200"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465A4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>30960</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>56160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>220320</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>140400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="テキスト枠 10"/>
+      <xdr:rowOff>113040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="テキスト枠 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4434480" y="896400"/>
+          <a:off x="3783240" y="869040"/>
           <a:ext cx="189360" cy="219240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1115,6 +1219,7 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
@@ -1124,11 +1229,6 @@
             </a:rPr>
             <a:t>*</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif CJK JP"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1137,65 +1237,30 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>7920</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>154080</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>801000</xdr:colOff>
+      <xdr:colOff>694080</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>150480</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="線 7"/>
-        <xdr:cNvSpPr/>
+      <xdr:rowOff>79920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>70560</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>136440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="テキスト枠 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3760200" y="966960"/>
-          <a:ext cx="793080" cy="880200"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="3465A4"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>30960</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>56160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>220320</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>113040</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="テキスト枠 11"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3783240" y="869040"/>
+          <a:off x="4446360" y="1776600"/>
           <a:ext cx="189360" cy="219240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1210,6 +1275,7 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
@@ -1219,11 +1285,6 @@
             </a:rPr>
             <a:t>*</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif CJK JP"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1231,26 +1292,85 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1642997</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>2402</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>694080</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>79920</xdr:rowOff>
+      <xdr:colOff>774242</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>167601</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="線 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{063D480F-E94C-4DD4-ACFC-6A3FC6778F05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3639630" y="2027972"/>
+          <a:ext cx="785460" cy="840388"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465A4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>652902</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>6660</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>70560</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>136440</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="テキスト枠 12"/>
+      <xdr:colOff>51325</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>27901</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="テキスト枠 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66B578E5-99C9-489D-9520-F79A6A8F02BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4446360" y="1776600"/>
-          <a:ext cx="189360" cy="219240"/>
+          <a:off x="4303750" y="2876217"/>
+          <a:ext cx="189360" cy="190038"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1264,6 +1384,63 @@
         <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Noto Serif CJK JP"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>86563</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>69335</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>253980</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>77165</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="テキスト枠 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{313823AF-8B5D-47F1-8E82-1A60319A58A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3737411" y="1926107"/>
+          <a:ext cx="167417" cy="345425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
@@ -1273,11 +1450,118 @@
             </a:rPr>
             <a:t>*</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif CJK JP"/>
-          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>401589</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>11806</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>698420</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>9825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="テキスト枠 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49B102B3-63DF-4EF4-9C5B-3CB3A8ABC869}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1443311" y="1193388"/>
+          <a:ext cx="296831" cy="166817"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Noto Serif CJK JP"/>
+            </a:rPr>
+            <a:t>0..*</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>519851</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>159722</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>24851</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>47805</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="テキスト枠 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2019153F-3321-4C7A-AF3E-CF637C4F58AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4170699" y="1003709"/>
+          <a:ext cx="295937" cy="225678"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Noto Serif CJK JP"/>
+            </a:rPr>
+            <a:t>0..*</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1287,7 +1571,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
@@ -1329,14 +1613,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -1389,26 +1673,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25.41"/>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1416,7 +1699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1436,7 +1719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1456,7 +1739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -1476,7 +1759,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1494,7 +1777,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
@@ -1512,7 +1795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:7">
       <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
@@ -1523,7 +1806,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -1537,7 +1820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
@@ -1548,7 +1831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
@@ -1562,7 +1845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
@@ -1580,7 +1863,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:7">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -1600,29 +1883,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>31</v>
+    <row r="13" spans="1:7">
+      <c r="A13" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:7">
       <c r="A14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>3</v>
@@ -1630,10 +1913,13 @@
       <c r="C15" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>3</v>
@@ -1641,15 +1927,43 @@
       <c r="C16" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="E16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="3:6">
+      <c r="E17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6">
       <c r="C18" s="7"/>
+      <c r="E18" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6">
+      <c r="E19" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <phoneticPr fontId="7"/>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
   </headerFooter>
